--- a/output/pdf_financials_xlsx/NOB.xlsx
+++ b/output/pdf_financials_xlsx/NOB.xlsx
@@ -6694,49 +6694,49 @@
         <v>2.852854</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.401866</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>8.849885</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>9.855354999999999</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>11.368796</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>11.449496</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>13.111438</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>13.111438</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>13.651056</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>13.801082</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>11.332732</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>11.599801</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.5375</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.812073</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.964645</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>3.001118</v>
       </c>
     </row>
     <row r="93">
@@ -10866,7 +10866,11 @@
           <t>Share-based payments and expired warrants reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -11670,7 +11674,11 @@
           <t>Share-based payments and expired warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -12176,7 +12184,11 @@
           <t>Share-based payments and expired warrants reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -14186,7 +14198,11 @@
           <t>Share-based payments and expired warrants reserve (Note 8(b))</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -15548,7 +15564,11 @@
           <t>Share-based and expired warrants reserve (Note 14(b))</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -17572,7 +17592,11 @@
           <t>Share-based and expired warrants reserve (Note 21(b))</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -19374,7 +19398,11 @@
           <t>Share-based and expired warrants reserve (Note 19(b))</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -21060,7 +21088,11 @@
           <t>Share-based and expired warrants reserve (Note 15(b))</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -23080,7 +23112,11 @@
           <t>Reserves 8,849,885</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NOB.xlsx
+++ b/output/pdf_financials_xlsx/NOB.xlsx
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.101122</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.009093</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00163</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000333</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-10.470272</v>
+        <v>-10.571394</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.876236</v>
+        <v>-2.885329</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.780188</v>
+        <v>-1.781818</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.405539</v>
+        <v>-2.405872</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-2.267278</v>
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-10.470272</v>
+        <v>-10.571394</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.876236</v>
+        <v>-2.885329</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.780188</v>
+        <v>-1.781818</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.405539</v>
+        <v>-2.405872</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.267278</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-722384.084084084</v>
+        <v>-722484.084084084</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E301" s="5" t="n">
@@ -47006,7 +47006,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -48594,7 +48594,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -49244,7 +49244,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -50422,7 +50422,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E393" s="5" t="n">

--- a/output/pdf_financials_xlsx/NOB.xlsx
+++ b/output/pdf_financials_xlsx/NOB.xlsx
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>0.01925</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.958792</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1894,10 +1894,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-9.511480000000001</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
@@ -2138,7 +2136,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-10.470272</v>
+        <v>-9.511480000000001</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-2.876236</v>
@@ -2351,7 +2349,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>174.504533</v>
+        <v>158.524667</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>95.874533</v>
@@ -2742,7 +2740,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-9.157278817589457</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -5066,10 +5064,10 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.136998</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="L67" s="3" t="n">
         <v>0</v>
@@ -7080,7 +7078,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-10.470272</v>
+        <v>-9.511480000000001</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-2.876236</v>
@@ -7830,10 +7828,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.043443</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.017444</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7878,7 +7876,7 @@
         <v>0</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="S111" s="3" t="n">
         <v>0</v>
@@ -8013,7 +8011,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.362166</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -9273,10 +9271,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.043443</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.017444</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -9321,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="S134" s="3" t="n">
         <v>0</v>
@@ -9334,10 +9332,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-4.140632</v>
+        <v>-4.184075</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.341564</v>
+        <v>-0.359008</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.6178090000000001</v>
@@ -9382,7 +9380,7 @@
         <v>-1.169697</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-0.9673850000000001</v>
+        <v>-0.982385</v>
       </c>
       <c r="S135" s="3" t="n">
         <v>-0.547896</v>
@@ -25538,7 +25536,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -27130,7 +27132,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -34354,7 +34360,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E241" s="5" t="n">
         <v>-0.362166</v>
       </c>
@@ -34562,7 +34572,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E243" s="5" t="n">
         <v>-0.043443</v>
       </c>
@@ -49030,7 +49044,11 @@
           <t>Directors' fees 27,750</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -53250,7 +53268,11 @@
           <t>Future income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E420" s="5" t="n">
         <v>-0.958792</v>
       </c>
